--- a/results/trace_full_merged_greedy_temp06_3b7b_results.xlsx
+++ b/results/trace_full_merged_greedy_temp06_3b7b_results.xlsx
@@ -12,12 +12,7 @@
     <sheet name="7b_greedy" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="7b_temp06" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3b_greedy'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3b_temp06'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'7b_greedy'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'7b_temp06'!$A$1:$K$33</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,27 +31,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -77,17 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,72 +430,59 @@
   </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suite</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>benchmark_key</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>benchmark</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dataset_alias</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prompt_run</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>grpo_step500_score</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>delta_grpo_minus_base</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>model_family</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decoding</t>
         </is>
@@ -555,13 +517,13 @@
       <c r="F2" t="n">
         <v>1000</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>19.4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>22.1</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>2.7</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -604,13 +566,13 @@
       <c r="F3" t="n">
         <v>2633</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>22.7497</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>23.8511</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>1.1014</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -653,13 +615,13 @@
       <c r="F4" t="n">
         <v>1272</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>72.7201</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>61.8711</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>-10.8491</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -702,13 +664,13 @@
       <c r="F5" t="n">
         <v>1581</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>19.8608</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>11.4485</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>-8.4124</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -751,13 +713,13 @@
       <c r="F6" t="n">
         <v>1948</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>34.2922</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>34.2128</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>-0.0794</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -800,13 +762,13 @@
       <c r="F7" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>31.4</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>40</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>8.6</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,13 +811,13 @@
       <c r="F8" t="n">
         <v>191</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>74.3455</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>74.8691</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>0.5236</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -898,13 +860,13 @@
       <c r="F9" t="n">
         <v>447</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>40.4922</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>42.7293</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>2.2371</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,13 +909,13 @@
       <c r="F10" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>62.1</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>65.59999999999999</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>3.5</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -996,13 +958,13 @@
       <c r="F11" t="n">
         <v>1200</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>65.83329999999999</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>72.41670000000001</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>6.5833</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -1045,13 +1007,13 @@
       <c r="F12" t="n">
         <v>1740</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>51.092</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>59.9425</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>8.8506</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -1094,13 +1056,13 @@
       <c r="F13" t="n">
         <v>3040</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>22.4671</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>26.3816</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>3.9145</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -1143,13 +1105,13 @@
       <c r="F14" t="n">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>38</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>35.5</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>-2.5</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -1192,13 +1154,13 @@
       <c r="F15" t="n">
         <v>405</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>39.7531</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>41.2346</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>1.4815</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1241,13 +1203,13 @@
       <c r="F16" t="n">
         <v>487</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>71.2526</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>72.4846</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>1.232</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -1290,13 +1252,13 @@
       <c r="F17" t="n">
         <v>788</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>17.8934</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>21.5736</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>3.6802</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -1339,13 +1301,13 @@
       <c r="F18" t="n">
         <v>1000</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>32.7</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>36.7</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -1388,13 +1350,13 @@
       <c r="F19" t="n">
         <v>1000</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>33.2</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>35.6</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>2.4</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -1437,13 +1399,13 @@
       <c r="F20" t="n">
         <v>1297</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>21.0486</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>20.9715</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>-0.0771</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -1486,13 +1448,13 @@
       <c r="F21" t="n">
         <v>1730</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>29.0173</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>30.289</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>1.2717</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -1535,13 +1497,13 @@
       <c r="F22" t="n">
         <v>1901</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>48.9742</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" t="n">
         <v>49.7633</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>0.7891</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -1584,13 +1546,13 @@
       <c r="F23" t="n">
         <v>2782</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>19.4824</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" t="n">
         <v>19.9497</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="n">
         <v>0.4673</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -1633,13 +1595,13 @@
       <c r="F24" t="n">
         <v>1000</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" t="n">
         <v>12.5002</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" t="n">
         <v>13.7776</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>1.2774</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1682,13 +1644,13 @@
       <c r="F25" t="n">
         <v>501</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>35.1113</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" t="n">
         <v>35.2545</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="n">
         <v>0.1432</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -1731,13 +1693,13 @@
       <c r="F26" t="n">
         <v>1168</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>19.2637</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="n">
         <v>17.637</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>-1.6267</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -1780,13 +1742,13 @@
       <c r="F27" t="n">
         <v>1528</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>15.9031</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" t="n">
         <v>15.3141</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="n">
         <v>-0.589</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -1829,13 +1791,13 @@
       <c r="F28" t="n">
         <v>1009</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>17.8394</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" t="n">
         <v>17.9386</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>0.09909999999999999</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -1878,13 +1840,13 @@
       <c r="F29" t="n">
         <v>1180</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" t="n">
         <v>21.5254</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" t="n">
         <v>27.7119</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>6.1864</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -1927,13 +1889,13 @@
       <c r="F30" t="n">
         <v>1290</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>3.3333</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" t="n">
         <v>4.1085</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>0.7752</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -1976,13 +1938,13 @@
       <c r="F31" t="n">
         <v>1500</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" t="n">
         <v>74.5067</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>2.8267</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -1997,69 +1959,68 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>average</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="5" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>35.5077</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" t="n">
         <v>36.8579</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" t="n">
         <v>1.3502</v>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>average_excl_screenspot</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Average excl. ScreenSpot</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>34.7375</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" t="n">
         <v>36.8721</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" t="n">
         <v>2.1346</v>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2072,72 +2033,59 @@
   </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suite</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>benchmark_key</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>benchmark</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dataset_alias</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prompt_run</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>grpo_step500_score</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>delta_grpo_minus_base</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>model_family</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decoding</t>
         </is>
@@ -2172,14 +2120,14 @@
       <c r="F2" t="n">
         <v>1000</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
+      <c r="G2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.199999999999999</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2221,13 +2169,13 @@
       <c r="F3" t="n">
         <v>2633</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>18.9897</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>20.7748</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>1.785</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -2270,13 +2218,13 @@
       <c r="F4" t="n">
         <v>1272</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>54.3239</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>4.3239</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -2319,13 +2267,13 @@
       <c r="F5" t="n">
         <v>1581</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>10.4364</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>10.4364</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -2368,13 +2316,13 @@
       <c r="F6" t="n">
         <v>1948</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>32.4924</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>33.2681</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>0.7756999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -2417,13 +2365,13 @@
       <c r="F7" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>33.55</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>42.55</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -2466,13 +2414,13 @@
       <c r="F8" t="n">
         <v>191</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>70.1571</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>72.7749</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>2.6178</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -2515,13 +2463,13 @@
       <c r="F9" t="n">
         <v>447</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>35.5705</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>42.2819</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>6.7114</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -2564,13 +2512,13 @@
       <c r="F10" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>61.9</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>4.7</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -2613,13 +2561,13 @@
       <c r="F11" t="n">
         <v>1200</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>57.1667</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>64.16670000000001</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -2662,13 +2610,13 @@
       <c r="F12" t="n">
         <v>1740</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>47.7011</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>59.1954</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>11.4943</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -2711,13 +2659,13 @@
       <c r="F13" t="n">
         <v>3040</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>19.8684</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>25.2632</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>5.3947</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -2760,13 +2708,13 @@
       <c r="F14" t="n">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>33.25</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>34</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>0.75</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -2809,13 +2757,13 @@
       <c r="F15" t="n">
         <v>405</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>38.2716</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>39.7531</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>1.4815</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -2858,13 +2806,13 @@
       <c r="F16" t="n">
         <v>487</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>68.7885</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>70.0205</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>1.232</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -2907,13 +2855,13 @@
       <c r="F17" t="n">
         <v>788</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>19.0355</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>21.3198</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>2.2843</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -2956,13 +2904,13 @@
       <c r="F18" t="n">
         <v>1000</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>29.9</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>33.7</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>3.8</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -3005,13 +2953,13 @@
       <c r="F19" t="n">
         <v>1000</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>32.9</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>37.1</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>4.2</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -3054,13 +3002,13 @@
       <c r="F20" t="n">
         <v>1297</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>21.6654</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>20.8944</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>-0.771</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -3103,13 +3051,13 @@
       <c r="F21" t="n">
         <v>1730</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>26.9364</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>31.7919</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>4.8555</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -3152,13 +3100,13 @@
       <c r="F22" t="n">
         <v>1901</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>44.5555</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" t="n">
         <v>46.5018</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>1.9463</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -3201,13 +3149,13 @@
       <c r="F23" t="n">
         <v>2782</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>23.5083</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" t="n">
         <v>23.7958</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="n">
         <v>0.2876</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -3250,13 +3198,13 @@
       <c r="F24" t="n">
         <v>1000</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" t="n">
         <v>12.4463</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" t="n">
         <v>13.613</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>1.1667</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -3299,13 +3247,13 @@
       <c r="F25" t="n">
         <v>501</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>32.7785</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" t="n">
         <v>33.7902</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="n">
         <v>1.0117</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -3348,13 +3296,13 @@
       <c r="F26" t="n">
         <v>1168</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>16.0959</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="n">
         <v>18.5788</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>2.4829</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -3397,13 +3345,13 @@
       <c r="F27" t="n">
         <v>1528</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>15.7068</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" t="n">
         <v>16.6885</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="n">
         <v>0.9817</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -3446,13 +3394,13 @@
       <c r="F28" t="n">
         <v>1009</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>16.1546</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" t="n">
         <v>18.5332</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>2.3786</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -3495,13 +3443,13 @@
       <c r="F29" t="n">
         <v>1180</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" t="n">
         <v>25.8475</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" t="n">
         <v>26.7797</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>0.9322</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -3544,13 +3492,13 @@
       <c r="F30" t="n">
         <v>1290</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>4.031</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" t="n">
         <v>4.8837</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>0.8527</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -3593,13 +3541,13 @@
       <c r="F31" t="n">
         <v>1500</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>68.4533</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" t="n">
         <v>71.30670000000001</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>2.8533</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -3614,69 +3562,68 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>average</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="5" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>32.2719</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" t="n">
         <v>35.1562</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" t="n">
         <v>2.8843</v>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>average_excl_screenspot</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Average excl. ScreenSpot</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>32.4186</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" t="n">
         <v>35.3545</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" t="n">
         <v>2.9359</v>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3689,72 +3636,59 @@
   </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suite</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>benchmark_key</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>benchmark</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dataset_alias</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prompt_run</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>grpo_step500_score</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>delta_grpo_minus_base</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>model_family</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decoding</t>
         </is>
@@ -3789,13 +3723,13 @@
       <c r="F2" t="n">
         <v>1000</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>25.6</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>33.6</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>8</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -3838,13 +3772,13 @@
       <c r="F3" t="n">
         <v>2633</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>26.3957</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>28.4466</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>2.0509</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -3887,13 +3821,13 @@
       <c r="F4" t="n">
         <v>1272</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>75.7075</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>79.55970000000001</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>3.8522</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -3936,13 +3870,13 @@
       <c r="F5" t="n">
         <v>1581</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>13.9152</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>11.7647</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>-2.1505</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -3985,13 +3919,13 @@
       <c r="F6" t="n">
         <v>1948</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>46.993</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>49.8713</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>2.8783</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -4034,13 +3968,13 @@
       <c r="F7" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>46.85</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>53.2</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>6.35</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -4083,13 +4017,13 @@
       <c r="F8" t="n">
         <v>191</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>76.43980000000001</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>73.822</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>-2.6178</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -4132,13 +4066,13 @@
       <c r="F9" t="n">
         <v>447</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>45.1902</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>48.0984</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>2.9083</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -4181,13 +4115,13 @@
       <c r="F10" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>69.7</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>74.2</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>4.5</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -4230,13 +4164,13 @@
       <c r="F11" t="n">
         <v>1200</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>75.58329999999999</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>81.75</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>6.1667</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -4279,13 +4213,13 @@
       <c r="F12" t="n">
         <v>1740</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>64.2529</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>67.3563</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>3.1034</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -4328,13 +4262,13 @@
       <c r="F13" t="n">
         <v>3040</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>26.0197</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>27.4342</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>1.4145</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -4377,13 +4311,13 @@
       <c r="F14" t="n">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>40.25</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>40.5</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>0.25</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -4426,13 +4360,13 @@
       <c r="F15" t="n">
         <v>405</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>41.4815</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>44.1975</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>2.716</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -4475,13 +4409,13 @@
       <c r="F16" t="n">
         <v>487</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>87.0637</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>86.2423</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>-0.8214</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -4524,13 +4458,13 @@
       <c r="F17" t="n">
         <v>788</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>22.9695</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>25</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>2.0305</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -4573,13 +4507,13 @@
       <c r="F18" t="n">
         <v>1000</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>42.6</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>47.2</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>4.6</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -4622,13 +4556,13 @@
       <c r="F19" t="n">
         <v>1000</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>40.8</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>48.6</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>7.8</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -4671,13 +4605,13 @@
       <c r="F20" t="n">
         <v>1297</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>20.5089</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>26.6769</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>6.1681</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -4720,13 +4654,13 @@
       <c r="F21" t="n">
         <v>1730</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>38.0347</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>40.4624</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>2.4277</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -4769,13 +4703,13 @@
       <c r="F22" t="n">
         <v>1901</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>56.3388</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" t="n">
         <v>59.3898</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>3.051</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -4818,13 +4752,13 @@
       <c r="F23" t="n">
         <v>2782</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>21.6751</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" t="n">
         <v>24.1193</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="n">
         <v>2.4443</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -4867,13 +4801,13 @@
       <c r="F24" t="n">
         <v>1000</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" t="n">
         <v>14.2257</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" t="n">
         <v>14.4972</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>0.2715</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -4916,13 +4850,13 @@
       <c r="F25" t="n">
         <v>501</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>37.3614</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" t="n">
         <v>36.3499</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="n">
         <v>-1.0115</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -4965,13 +4899,13 @@
       <c r="F26" t="n">
         <v>1168</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>19.863</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="n">
         <v>20.2055</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>0.3425</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -5014,13 +4948,13 @@
       <c r="F27" t="n">
         <v>1528</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>22.7749</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" t="n">
         <v>22.1859</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="n">
         <v>-0.589</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -5063,13 +4997,13 @@
       <c r="F28" t="n">
         <v>1009</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>18.8305</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" t="n">
         <v>20.0198</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>1.1893</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -5112,13 +5046,13 @@
       <c r="F29" t="n">
         <v>1180</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" t="n">
         <v>26.3559</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" t="n">
         <v>29.4068</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>3.0508</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -5161,13 +5095,13 @@
       <c r="F30" t="n">
         <v>1290</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>5.969</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" t="n">
         <v>6.0465</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>0.0775</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -5210,13 +5144,13 @@
       <c r="F31" t="n">
         <v>1500</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>77.44</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" t="n">
         <v>79.2</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>1.76</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -5231,69 +5165,68 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>average</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="5" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>40.9063</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" t="n">
         <v>43.3134</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" t="n">
         <v>2.4071</v>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>average_excl_screenspot</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Average excl. ScreenSpot</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>40.6274</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" t="n">
         <v>43.1457</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" t="n">
         <v>2.5183</v>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5306,72 +5239,59 @@
   </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suite</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>benchmark_key</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>benchmark</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dataset_alias</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prompt_run</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>grpo_step500_score</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>delta_grpo_minus_base</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>model_family</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decoding</t>
         </is>
@@ -5406,14 +5326,14 @@
       <c r="F2" t="n">
         <v>1000</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.1</v>
+      <c r="G2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.799999999999997</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5455,13 +5375,13 @@
       <c r="F3" t="n">
         <v>2633</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>25.0665</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" t="n">
         <v>29.0923</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="n">
         <v>4.0258</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -5504,13 +5424,13 @@
       <c r="F4" t="n">
         <v>1272</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>77.12260000000001</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>77.8302</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>0.7075</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -5553,13 +5473,13 @@
       <c r="F5" t="n">
         <v>1581</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>13.4092</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>10.2467</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>-3.1626</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -5602,13 +5522,13 @@
       <c r="F6" t="n">
         <v>1948</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>46.3831</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" t="n">
         <v>49.5933</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>3.2102</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -5651,13 +5571,13 @@
       <c r="F7" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>46.7</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" t="n">
         <v>53.4</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>6.7</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -5700,13 +5620,13 @@
       <c r="F8" t="n">
         <v>191</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>75.3927</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>75.9162</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>0.5236</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -5749,13 +5669,13 @@
       <c r="F9" t="n">
         <v>447</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>42.5056</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" t="n">
         <v>48.5459</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>6.0403</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -5798,13 +5718,13 @@
       <c r="F10" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>69.3</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" t="n">
         <v>73.3</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -5847,13 +5767,13 @@
       <c r="F11" t="n">
         <v>1200</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>76.08329999999999</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>81.91670000000001</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>5.8333</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -5896,13 +5816,13 @@
       <c r="F12" t="n">
         <v>1740</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>64.5402</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" t="n">
         <v>67.5287</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>2.9885</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -5945,13 +5865,13 @@
       <c r="F13" t="n">
         <v>3040</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>25.3289</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" t="n">
         <v>28.5526</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>3.2237</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -5994,13 +5914,13 @@
       <c r="F14" t="n">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>39.75</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>40.75</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -6043,13 +5963,13 @@
       <c r="F15" t="n">
         <v>405</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>39.2593</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" t="n">
         <v>42.716</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="n">
         <v>3.4568</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -6092,13 +6012,13 @@
       <c r="F16" t="n">
         <v>487</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>83.5729</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" t="n">
         <v>85.83159999999999</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>2.2587</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -6141,13 +6061,13 @@
       <c r="F17" t="n">
         <v>788</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>25.2538</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>24.7462</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="n">
         <v>-0.5076000000000001</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -6190,13 +6110,13 @@
       <c r="F18" t="n">
         <v>1000</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>38.5</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" t="n">
         <v>45.5</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -6239,13 +6159,13 @@
       <c r="F19" t="n">
         <v>1000</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>38.1</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="n">
         <v>46.1</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="n">
         <v>8</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -6288,13 +6208,13 @@
       <c r="F20" t="n">
         <v>1297</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>22.2822</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>24.3639</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>2.0817</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -6337,13 +6257,13 @@
       <c r="F21" t="n">
         <v>1730</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" t="n">
         <v>35.3757</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" t="n">
         <v>40.3468</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>4.9711</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -6386,13 +6306,13 @@
       <c r="F22" t="n">
         <v>1901</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>53.2877</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" t="n">
         <v>58.6533</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>5.3656</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -6435,13 +6355,13 @@
       <c r="F23" t="n">
         <v>2782</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>24.335</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" t="n">
         <v>23.1848</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="n">
         <v>-1.1503</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -6484,13 +6404,13 @@
       <c r="F24" t="n">
         <v>1000</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" t="n">
         <v>15.0191</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" t="n">
         <v>14.3645</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>-0.6546</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -6533,13 +6453,13 @@
       <c r="F25" t="n">
         <v>501</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>38.4801</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" t="n">
         <v>38.0125</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="n">
         <v>-0.4675</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -6582,13 +6502,13 @@
       <c r="F26" t="n">
         <v>1168</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>18.2363</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="n">
         <v>20.5479</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>2.3116</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -6631,13 +6551,13 @@
       <c r="F27" t="n">
         <v>1528</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>20.7461</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" t="n">
         <v>21.9241</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="n">
         <v>1.178</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -6680,13 +6600,13 @@
       <c r="F28" t="n">
         <v>1009</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>19.6234</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" t="n">
         <v>19.3261</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>-0.2973</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -6729,13 +6649,13 @@
       <c r="F29" t="n">
         <v>1180</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" t="n">
         <v>26.1017</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" t="n">
         <v>31.0169</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>4.9153</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -6778,13 +6698,13 @@
       <c r="F30" t="n">
         <v>1290</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>5.8915</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" t="n">
         <v>6.4341</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>0.5426</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -6827,13 +6747,13 @@
       <c r="F31" t="n">
         <v>1500</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>73.6267</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" t="n">
         <v>78.13330000000001</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>4.5067</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -6848,69 +6768,68 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>average</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="5" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>39.3125</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" t="n">
         <v>41.9292</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" t="n">
         <v>2.6167</v>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>average_excl_screenspot</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Average excl. ScreenSpot</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>38.8872</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" t="n">
         <v>41.7785</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" t="n">
         <v>2.8913</v>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>